--- a/resultados/altonia/inventario_externos.xlsx
+++ b/resultados/altonia/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3260,6 +3260,2097 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>http://201.87.233.17:5620/pronimtb/index.asp?acao=1&amp;item=2</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>201.87.233.17:5620</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/10720_Leilao-Publico-001-2019.html</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>4</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:33:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>http://www.exatuspr.com.br/novo/concurso/pmaltonia0012018</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>www.exatuspr.com.br</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Exatus Consultoria (AVR Assessoria Técnica Ltda – EPP)</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/9974_Concurso-001-2018.html</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>4</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:33:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Copa-Alt%C3%B4nia-de-Futsal-176747129187712/</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>página</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/9197_Copa-Altonia-Futsal-2019.html</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>4</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:34:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>http://online.fliphtml5.com/vrgn/aunu/?fbclid=IwAR0ccUuO0G0g2dr1cXdnpis0n_iow-2GTU0MzgmSvQeeYFRaEKMF2myclXw</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>online.fliphtml5.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Veja a Revista 50 Anos na íntegra online [aqui]</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/10069_Revista-Altonia-50-Anos.html</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>4</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:34:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>http://www.ecobooking.com.br</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>www.ecobooking.com.br</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>www.ecobooking.com.br</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/8303_7-Edicao-da-Caminhada-na-Natureza.html</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>4</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:35:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://m.facebook.com/hashtag/vacinar%C3%A9proteger?refid=52&amp;__tn__=%2As-R</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>m.facebook.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>#VacinarÉProteger</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/8446_Campanha-Nacional-de-Vacinacao-contra-a-Polio-e-o-Sarampo.html</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>4</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:35:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/auniaofazavida/?fref=mentions</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Programa A União Faz a Vida</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/8389_Gervasone-recebe-no-gabinete-alunos.html</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>4</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:35:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>http://ecobooking.com.br</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ecobooking.com.br</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ecobooking.com.br</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/7869_Altonia-realiza-neste-Final-de-Semana-a-7-Edicao-da-Caminhada-na-Natureza.html</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>4</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:37:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>http://www.institutofip.com.br/concurso/ALTONIA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>www.institutofip.com.br</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Instituto FIP</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/7143_Teste-Seletivo-Edital-0012018-Abertura.html</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>4</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:37:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>http://www.institutofip.com.br/</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>www.institutofip.com.br</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/7143_Teste-Seletivo-Edital-0012018-Abertura.html</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>4</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:37:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>http://www.institutofip.com.br/sistema/uploads/EDITALABERTURA_1.pdf</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>www.institutofip.com.br</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Altônia - Edital de Abertura</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/7143_Teste-Seletivo-Edital-0012018-Abertura.html</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>4</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:37:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>http://www.institutofip.com.br/sistema/uploads/resultado_pedido_isencao.pdf</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>www.institutofip.com.br</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Altônia - Resultado Pedido de Isenção</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/7143_Teste-Seletivo-Edital-0012018-Abertura.html</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>4</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:37:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>http://www.institutofip.com.br/sistema/uploads/homologacao_ensalamento_inscricao.pdf</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>www.institutofip.com.br</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Altônia - Edital de Homologação das Inscrições</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/7143_Teste-Seletivo-Edital-0012018-Abertura.html</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>4</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:37:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>http://www.institutofip.com.br/sistema/uploads/ensalamento.pdf</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>www.institutofip.com.br</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Altônia - Ensalamento</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/7143_Teste-Seletivo-Edital-0012018-Abertura.html</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>4</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:37:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>http://www.institutofip.com.br/sistema/uploads/FORMULARIO_DE_ENTREGA_DE_TITULO.pdf</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>www.institutofip.com.br</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Formulário de Entrega de Títulos</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/7143_Teste-Seletivo-Edital-0012018-Abertura.html</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>4</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:37:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>http://www.institutofip.com.br/sistema/uploads/GABARITO_PRELIMINAR_3.pdf</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>www.institutofip.com.br</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Altônia - Gabarito Preliminar</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/7143_Teste-Seletivo-Edital-0012018-Abertura.html</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>4</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:37:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://apps.tre-pr.jus.br/agendamento/publico/registrarAgendamentoEleitor.do?acao=load</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>apps.tre-pr.jus.br</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://apps.tre-pr.jus.br/agendamento/publico/registrarAgendamentoEleitor.do?acao=load</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/6603_Autoridades-participam-de-reuniao-com-Desembargador-do-TRE-sobre-a-Biometria.html</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>4</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:38:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>http://apps.tre-pr.jus.br/agendamento/publico/registrarAgendamentoEleitor.do?acao=load</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>apps.tre-pr.jus.br</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Agendamento de Atendimento ao Eleitor</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/6447_Recadastramento-Biometrico-para-os-Eleitores-de-Altonia-e-Sao-Jorge-do-Patrocinio.html</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>4</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:38:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>http://www.tre-pr.jus.br/imprensa/noticias-tre-pr/2017/Setembro/expansao-da-biometria-no-parana-alcanca-mais-26-cidades</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>www.tre-pr.jus.br</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Expansão da biometria no Paraná alcança mais 26 cidades</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/6447_Recadastramento-Biometrico-para-os-Eleitores-de-Altonia-e-Sao-Jorge-do-Patrocinio.html</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>4</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:38:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://chrome.google.com/webstore/detail/data-saver/pfmgfdlgomnbgkofeojodiodmgpgmkac?hl=pt-BR</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>chrome.google.com</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ERR_EMPTY_RESPONSE</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/5735_Erro-ao-abrir-NFs-ERREMPTYRESPONSE.html</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>4</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:39:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>http://combateaedes.saude.gov.br/</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>combateaedes.saude.gov.br</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Dengue, Chikungunya e Zika</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/3619_Dengue-Chikungunya-e-Zika.html</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>4</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:41:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/copaaltonia2016</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>#copaaltonia2016</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/3371_Copa-Altonia-de-Futsal-2016.html</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>4</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:42:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/amelhordoparana</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>#amelhordoparana</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/3371_Copa-Altonia-de-Futsal-2016.html</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>4</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:42:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>http://www.ruffoconcursos.com.br/concurso/25/Prefeitura-Municipal-de-Altonia-001-2015</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>www.ruffoconcursos.com.br</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>www.ruffoconcursos.com.br</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/3134_Prefeitura-de-Altonia-PR-reabre-inscricoes-de-Concurso-Publico.html</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>4</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:42:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>http://www.confiraconcursos.com/leitor-pdf/?edital=DBs3Fg</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>www.confiraconcursos.com</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Clique aqui</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/2919_Altonia-realiza-concurso-para-54-vagas.html</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>4</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:43:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>http://www.apostilasopcao.com.br/apostilas/798/1363/materias-para-concursos-publicos/matematica.php?afiliado=10526</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>www.apostilasopcao.com.br</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Confira apostilas para este concurso.</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/2919_Altonia-realiza-concurso-para-54-vagas.html</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>4</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:43:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>http://www.coripa.org.br/arquivos/ckEditor/files/Edital%20na%20integra(2).pdf</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>www.coripa.org.br</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>clique aqui.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/2709_ICMBio-Aberto-edital-para-eleicoes-dos-Membros-do-Conselho-Consultivo-do-Parque-Nacional-de-Ilha-Grande.html</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>4</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:43:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pages/Copa-Alt%C3%B4nia-de-Futsal/176747129187712?fref=nf</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pages/Copa-Alt%C3%B4nia-de-Futsal/176747129187712?fref=nf</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/1901_Copa-Altonia-de-Futsal-Semi-Final.html</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>4</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:44:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pages/Copa-Alt%C3%B4nia-de-Futsal/176747129187712</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pages/Copa-Alt%C3%B4nia-de-Futsal/176747129187712</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/1867_Copa-Altonia-2015.html</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>4</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:44:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/nanduh.rios</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Nanduh Rios</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/1423_Desfile-da-Primavera-Creches-de-Altonia.html</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>4</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:45:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>http://galerias.amerios.com.br/galeria/expedicao-na-apa-municipal-ec-cab-2014/</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>galerias.amerios.com.br</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Veja a Galeria de Fotos</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/1120_Expedicao-na-APA-Municipal-de-Altonia.html</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>4</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:45:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/encontrosecaminhoscab</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>#EncontroseCaminhosCAB</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/1120_Expedicao-na-APA-Municipal-de-Altonia.html</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>4</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:45:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/recantoportaldeluz</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Recanto Wakami Portal de Luz</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/1120_Expedicao-na-APA-Municipal-de-Altonia.html</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>4</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:45:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/josue.perrone.13</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Josué Emanuel</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/1120_Expedicao-na-APA-Municipal-de-Altonia.html</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>4</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:45:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ivypiaf</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Ivy Ribeiro</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/1120_Expedicao-na-APA-Municipal-de-Altonia.html</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>4</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:45:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>http://www.portalaltonia.com.br/?s=%23encontrosecaminhoscab&amp;x=16&amp;y=21</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>www.portalaltonia.com.br</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>#EncontroseCaminhosCAB</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/1120_Expedicao-na-APA-Municipal-de-Altonia.html</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>4</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:45:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>http://galerias.amerios.com.br/galeria/visitas-a-nascentes-restauradas-e-plantio-de-mudas/</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>galerias.amerios.com.br</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Veja a galeria de Fotos</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/1091_Visita-a-Nascentes-Restauradas-e-Plantio-de-Mudas-de-Arvores-em-Altonia.html</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>4</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:45:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>http://galerias.amerios.com.br/galeria/caminhadas-na-natureza-em-altonia/</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>galerias.amerios.com.br</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Veja a Galeria de Fotos</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/1029_Realizacao-da-3-Caminhada-Internacional-na-Natureza-em-Altonia.html</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>4</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:45:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/leticia.pereira.568294</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Letícia Pereira</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/1029_Realizacao-da-3-Caminhada-Internacional-na-Natureza-em-Altonia.html</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>4</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:45:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>http://galerias.amerios.com.br/galeria/teatros-e-exposicoes-na-mostra-cultural-em-altonia/</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>galerias.amerios.com.br</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Veja a Galeria de Fotos</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/993_Projeto-Encontros-e-Caminhos-Mostra-Cultural.html</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>4</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:45:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/carlosalexandre.azevedosolivo</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Carlos Alexandre</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/993_Projeto-Encontros-e-Caminhos-Mostra-Cultural.html</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>4</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:45:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>http://galerias.amerios.com.br/galeria/pec-cab-entrega-de-certificado-ambiental/</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>galerias.amerios.com.br</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Veja a Galeria de Fotos</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/1002_Projeto-Encontros-e-Caminhos-Certificados-de-Acoes-Praticas-Ambientais.html</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>4</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:45:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>http://encontrosecaminhoscab.com.br/</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>encontrosecaminhoscab.com.br</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>www.encontrosecaminhoscab.com.br</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/798_Projeto-Encontros-e-Caminhos.html</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>4</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:45:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://www.pr.senac.br/busca/?p=WORKSHOP%20-%20ATENDIMENTO%20PARA%20GAR%C3%87OM</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>www.pr.senac.br</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>www.pr.senac.br/umuarama</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/noticiasView/7546_Senac-e-Sala-do-Empreendedor-de-Altonia-promovem-curso-ATENDIMENTO-PARA-GARCOM.html</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>5</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:08:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>https://www.telegram.com/</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>www.telegram.com</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>https://www.whatsapp.com/</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>www.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>https://www.x.com/</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>www.x.com</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>https://www.governancabrasil.com.br/</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>www.governancabrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>https://www.volarisgroup.com/pt-br</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>www.volarisgroup.com</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Volaris Group</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/governodigital/pt-br/acessibilidade-digital/eMAGv31.pdf</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>www.gov.br</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Modelo de Acessibilidade em Governo Eletrônico - eMAG</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>https://www.w3.org/TR/WCAG21/</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>www.w3.org</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Web Content Accessibility Guidelines (em inglês)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>https://vlibras.gov.br/</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>vlibras.gov.br</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>VLibras</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>https://www.nvaccess.org/download/</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>www.nvaccess.org</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NVDA (em inglês)</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>https://support.freedomscientific.com/Downloads/JAWS</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>support.freedomscientific.com</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>JAWS (em inglês)</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>https://support.apple.com/pt-br/guide/voiceover/welcome/mac</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>support.apple.com</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>VoiceOver</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?text=</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>http://www.facebook.com/sharer.php?u=</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>https://twitter.com/share?text=</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>twitter.com</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/shareArticle?mini=true&amp;url=</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/acessibilidade</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
